--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/SOUTH_CAROLINA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/SOUTH_CAROLINA_2013.xlsx
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C217">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C549">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C652">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C688">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C689">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C694">
@@ -21192,7 +21192,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1158">
